--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$258</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7725" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8043" uniqueCount="614">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:39:31+00:00</t>
+    <t>2026-09-03T14:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1084,6 +1084,21 @@
     <t>Autre TemplateId</t>
   </si>
   <si>
+    <t>Organizer.participant:frParticipantResponsable.templateId:templateId-other.nullFlavor</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantResponsable.templateId:templateId-other.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantResponsable.templateId:templateId-other.displayable</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantResponsable.templateId:templateId-other.root</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantResponsable.templateId:templateId-other.extension</t>
+  </si>
+  <si>
     <t>Organizer.participant:frParticipantResponsable.typeCode</t>
   </si>
   <si>
@@ -1316,6 +1331,21 @@
   </si>
   <si>
     <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other.nullFlavor</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other.displayable</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other.root</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other.extension</t>
   </si>
   <si>
     <t>Organizer.participant:frParticipantDispositif.typeCode</t>
@@ -2198,7 +2228,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK248"/>
+  <dimension ref="A1:AK258"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="87.296875" customWidth="true" bestFit="true"/>
@@ -12912,26 +12942,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
         <v>345</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E106" s="2"/>
+      <c r="E106" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F106" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>75</v>
@@ -12943,7 +12975,9 @@
         <v>86</v>
       </c>
       <c r="L106" s="2"/>
-      <c r="M106" s="2"/>
+      <c r="M106" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -12954,7 +12988,7 @@
         <v>75</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>347</v>
+        <v>75</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>75</v>
@@ -12973,7 +13007,7 @@
       </c>
       <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>233</v>
+        <v>89</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>75</v>
@@ -12991,10 +13025,10 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>348</v>
+        <v>90</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>76</v>
@@ -13011,16 +13045,18 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E107" s="2"/>
+      <c r="E107" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F107" t="s" s="2">
         <v>81</v>
       </c>
@@ -13037,10 +13073,12 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L107" s="2"/>
-      <c r="M107" s="2"/>
+      <c r="M107" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13048,7 +13086,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>351</v>
+        <v>75</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>75</v>
@@ -13066,11 +13104,13 @@
         <v>75</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>352</v>
+        <v>75</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>75</v>
@@ -13088,7 +13128,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>353</v>
+        <v>105</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -13108,16 +13148,18 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E108" s="2"/>
+      <c r="E108" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F108" t="s" s="2">
         <v>81</v>
       </c>
@@ -13134,10 +13176,12 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="L108" s="2"/>
-      <c r="M108" s="2"/>
+      <c r="M108" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -13187,7 +13231,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>356</v>
+        <v>110</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -13207,18 +13251,20 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E109" s="2"/>
+      <c r="E109" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F109" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>76</v>
@@ -13233,13 +13279,11 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="L109" s="2"/>
       <c r="M109" t="s" s="2">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -13290,7 +13334,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>360</v>
+        <v>116</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -13310,17 +13354,17 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="F110" t="s" s="2">
         <v>81</v>
@@ -13338,11 +13382,11 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" t="s" s="2">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13369,11 +13413,13 @@
         <v>75</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y110" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z110" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>75</v>
@@ -13391,7 +13437,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -13409,12 +13455,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13422,13 +13468,13 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>75</v>
@@ -13437,12 +13483,10 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>365</v>
+        <v>86</v>
       </c>
       <c r="L111" s="2"/>
-      <c r="M111" t="s" s="2">
-        <v>366</v>
-      </c>
+      <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -13453,7 +13497,7 @@
         <v>75</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>75</v>
+        <v>352</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>75</v>
@@ -13468,13 +13512,11 @@
         <v>75</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>75</v>
+        <v>233</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -13492,10 +13534,10 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>76</v>
@@ -13512,10 +13554,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13541,17 +13583,15 @@
         <v>86</v>
       </c>
       <c r="L112" s="2"/>
-      <c r="M112" t="s" s="2">
-        <v>370</v>
-      </c>
+      <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
-        <v>371</v>
+        <v>75</v>
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>75</v>
+        <v>356</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>75</v>
@@ -13573,7 +13613,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>75</v>
@@ -13591,7 +13631,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -13609,20 +13649,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E113" t="s" s="2">
-        <v>376</v>
-      </c>
+      <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>81</v>
       </c>
@@ -13630,7 +13668,7 @@
         <v>76</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>75</v>
@@ -13639,12 +13677,10 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>377</v>
+        <v>279</v>
       </c>
       <c r="L113" s="2"/>
-      <c r="M113" t="s" s="2">
-        <v>378</v>
-      </c>
+      <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13694,7 +13730,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13712,20 +13748,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E114" t="s" s="2">
-        <v>382</v>
-      </c>
+      <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>81</v>
       </c>
@@ -13733,7 +13767,7 @@
         <v>76</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>75</v>
@@ -13742,11 +13776,13 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="L114" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="M114" t="s" s="2">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13797,7 +13833,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13817,17 +13853,17 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>387</v>
+        <v>85</v>
       </c>
       <c r="F115" t="s" s="2">
         <v>81</v>
@@ -13845,11 +13881,11 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>283</v>
+        <v>86</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" t="s" s="2">
-        <v>388</v>
+        <v>87</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13876,13 +13912,11 @@
         <v>75</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>75</v>
@@ -13900,7 +13934,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>389</v>
+        <v>90</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -13918,20 +13952,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E116" t="s" s="2">
-        <v>392</v>
-      </c>
+      <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>81</v>
       </c>
@@ -13939,7 +13971,7 @@
         <v>76</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>75</v>
@@ -13948,11 +13980,11 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" t="s" s="2">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14003,7 +14035,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -14023,10 +14055,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>396</v>
+        <v>374</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14049,14 +14081,16 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>279</v>
+        <v>86</v>
       </c>
       <c r="L117" s="2"/>
-      <c r="M117" s="2"/>
+      <c r="M117" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
-        <v>75</v>
+        <v>376</v>
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
@@ -14078,13 +14112,11 @@
         <v>75</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>75</v>
+        <v>377</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>75</v>
@@ -14102,7 +14134,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -14122,18 +14154,20 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E118" s="2"/>
+      <c r="E118" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="F118" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>76</v>
@@ -14148,13 +14182,11 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="L118" s="2"/>
       <c r="M118" t="s" s="2">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -14205,10 +14237,10 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>76</v>
@@ -14225,23 +14257,23 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E119" s="2"/>
+      <c r="E119" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="F119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>75</v>
@@ -14253,12 +14285,12 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="M119" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="L119" s="2"/>
+      <c r="M119" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -14308,13 +14340,13 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>302</v>
+        <v>389</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>75</v>
@@ -14328,17 +14360,17 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>310</v>
+        <v>391</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>85</v>
+        <v>392</v>
       </c>
       <c r="F120" t="s" s="2">
         <v>81</v>
@@ -14356,11 +14388,11 @@
         <v>75</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>86</v>
+        <v>283</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" t="s" s="2">
-        <v>87</v>
+        <v>393</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14387,11 +14419,13 @@
         <v>75</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y120" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z120" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>75</v>
@@ -14409,7 +14443,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>90</v>
+        <v>394</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -14427,26 +14461,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>312</v>
+        <v>396</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E121" s="2"/>
+      <c r="E121" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="F121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>75</v>
@@ -14455,11 +14491,11 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>92</v>
+        <v>382</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" t="s" s="2">
-        <v>93</v>
+        <v>398</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -14510,13 +14546,13 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>94</v>
+        <v>399</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>75</v>
@@ -14530,10 +14566,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>314</v>
+        <v>401</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14556,12 +14592,10 @@
         <v>75</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>96</v>
+        <v>279</v>
       </c>
       <c r="L122" s="2"/>
-      <c r="M122" t="s" s="2">
-        <v>97</v>
-      </c>
+      <c r="M122" s="2"/>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14611,7 +14645,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>98</v>
+        <v>402</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -14623,34 +14657,32 @@
         <v>75</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>316</v>
+        <v>404</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E123" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>75</v>
@@ -14659,11 +14691,13 @@
         <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L123" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="M123" t="s" s="2">
-        <v>87</v>
+        <v>406</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -14690,11 +14724,13 @@
         <v>75</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y123" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z123" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>75</v>
@@ -14712,10 +14748,10 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>90</v>
+        <v>407</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>76</v>
@@ -14732,40 +14768,40 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="D124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="B124" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E124" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L124" s="2"/>
-      <c r="M124" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="M124" s="2"/>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -14815,13 +14851,13 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>105</v>
+        <v>302</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>75</v>
@@ -14838,14 +14874,14 @@
         <v>411</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="F125" t="s" s="2">
         <v>81</v>
@@ -14863,11 +14899,11 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" t="s" s="2">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -14894,13 +14930,11 @@
         <v>75</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>75</v>
@@ -14918,7 +14952,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -14941,20 +14975,18 @@
         <v>412</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E126" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>75</v>
@@ -14966,11 +14998,11 @@
         <v>75</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" t="s" s="2">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14979,7 +15011,7 @@
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>75</v>
@@ -15021,13 +15053,13 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>75</v>
@@ -15044,17 +15076,15 @@
         <v>413</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E127" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>76</v>
@@ -15069,11 +15099,11 @@
         <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -15124,7 +15154,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -15136,7 +15166,7 @@
         <v>75</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>75</v>
@@ -15147,18 +15177,20 @@
         <v>414</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E128" s="2"/>
+      <c r="E128" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>75</v>
@@ -15170,13 +15202,11 @@
         <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L128" s="2"/>
       <c r="M128" t="s" s="2">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -15203,35 +15233,35 @@
         <v>75</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AC128" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>75</v>
@@ -15248,15 +15278,15 @@
         <v>415</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E129" s="2"/>
+      <c r="E129" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F129" t="s" s="2">
         <v>81</v>
       </c>
@@ -15273,13 +15303,11 @@
         <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="L129" s="2"/>
       <c r="M129" t="s" s="2">
-        <v>330</v>
+        <v>104</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -15330,13 +15358,13 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>75</v>
@@ -15353,14 +15381,14 @@
         <v>416</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="F130" t="s" s="2">
         <v>81</v>
@@ -15378,11 +15406,11 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -15409,11 +15437,13 @@
         <v>75</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y130" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z130" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>75</v>
@@ -15431,7 +15461,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -15454,17 +15484,17 @@
         <v>417</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F131" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>76</v>
@@ -15479,11 +15509,11 @@
         <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" t="s" s="2">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -15492,7 +15522,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>75</v>
@@ -15534,7 +15564,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -15557,17 +15587,17 @@
         <v>418</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F132" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>76</v>
@@ -15582,11 +15612,11 @@
         <v>75</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -15637,7 +15667,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -15660,20 +15690,18 @@
         <v>419</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E133" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>75</v>
@@ -15685,11 +15713,13 @@
         <v>75</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L133" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="M133" t="s" s="2">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15701,7 +15731,7 @@
         <v>75</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>339</v>
+        <v>75</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>75</v>
@@ -15728,25 +15758,23 @@
         <v>75</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="AC133" s="2"/>
       <c r="AD133" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>75</v>
@@ -15763,15 +15791,15 @@
         <v>420</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C134" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="D134" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E134" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>81</v>
       </c>
@@ -15788,11 +15816,13 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L134" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="M134" t="s" s="2">
-        <v>119</v>
+        <v>330</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15843,13 +15873,13 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>75</v>
@@ -15866,20 +15896,20 @@
         <v>421</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E135" s="2"/>
+      <c r="E135" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>75</v>
@@ -15891,13 +15921,11 @@
         <v>75</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L135" s="2"/>
       <c r="M135" t="s" s="2">
-        <v>344</v>
+        <v>87</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -15924,13 +15952,11 @@
         <v>75</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>75</v>
@@ -15948,13 +15974,13 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>75</v>
@@ -15966,26 +15992,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
         <v>422</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E136" s="2"/>
+      <c r="E136" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F136" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>75</v>
@@ -15994,10 +16022,12 @@
         <v>75</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L136" s="2"/>
-      <c r="M136" s="2"/>
+      <c r="M136" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -16008,7 +16038,7 @@
         <v>75</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>423</v>
+        <v>75</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>75</v>
@@ -16023,11 +16053,13 @@
         <v>75</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y136" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z136" t="s" s="2">
-        <v>233</v>
+        <v>75</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>75</v>
@@ -16045,10 +16077,10 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>348</v>
+        <v>105</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>76</v>
@@ -16065,16 +16097,18 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E137" s="2"/>
+      <c r="E137" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F137" t="s" s="2">
         <v>81</v>
       </c>
@@ -16091,10 +16125,12 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L137" s="2"/>
-      <c r="M137" s="2"/>
+      <c r="M137" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -16102,7 +16138,7 @@
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>351</v>
+        <v>75</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>75</v>
@@ -16120,11 +16156,13 @@
         <v>75</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y137" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z137" t="s" s="2">
-        <v>352</v>
+        <v>75</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>75</v>
@@ -16142,7 +16180,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>353</v>
+        <v>110</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -16162,18 +16200,20 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E138" s="2"/>
+      <c r="E138" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F138" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G138" t="s" s="2">
         <v>76</v>
@@ -16188,10 +16228,12 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>279</v>
+        <v>113</v>
       </c>
       <c r="L138" s="2"/>
-      <c r="M138" s="2"/>
+      <c r="M138" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -16202,7 +16244,7 @@
         <v>75</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>75</v>
+        <v>339</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>75</v>
@@ -16241,7 +16283,7 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>356</v>
+        <v>116</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -16259,18 +16301,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E139" s="2"/>
+      <c r="E139" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="F139" t="s" s="2">
         <v>81</v>
       </c>
@@ -16278,7 +16322,7 @@
         <v>76</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>75</v>
@@ -16287,13 +16331,11 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="L139" s="2"/>
       <c r="M139" t="s" s="2">
-        <v>359</v>
+        <v>119</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -16344,7 +16386,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -16364,23 +16406,23 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C140" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="D140" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E140" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>75</v>
@@ -16392,11 +16434,13 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L140" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="M140" t="s" s="2">
-        <v>87</v>
+        <v>344</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -16423,11 +16467,13 @@
         <v>75</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y140" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z140" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>75</v>
@@ -16445,13 +16491,13 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>75</v>
@@ -16465,16 +16511,18 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>364</v>
+        <v>332</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E141" s="2"/>
+      <c r="E141" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F141" t="s" s="2">
         <v>81</v>
       </c>
@@ -16491,11 +16539,11 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>365</v>
+        <v>86</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" t="s" s="2">
-        <v>366</v>
+        <v>87</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -16522,13 +16570,11 @@
         <v>75</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>75</v>
@@ -16546,7 +16592,7 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>367</v>
+        <v>90</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -16566,16 +16612,18 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E142" s="2"/>
+      <c r="E142" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F142" t="s" s="2">
         <v>81</v>
       </c>
@@ -16592,16 +16640,16 @@
         <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" t="s" s="2">
-        <v>370</v>
+        <v>104</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
-        <v>371</v>
+        <v>75</v>
       </c>
       <c r="Q142" s="2"/>
       <c r="R142" t="s" s="2">
@@ -16623,11 +16671,13 @@
         <v>75</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y142" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z142" t="s" s="2">
-        <v>372</v>
+        <v>75</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>75</v>
@@ -16645,7 +16695,7 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>373</v>
+        <v>105</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -16663,19 +16713,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>375</v>
+        <v>336</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E143" t="s" s="2">
-        <v>376</v>
+        <v>107</v>
       </c>
       <c r="F143" t="s" s="2">
         <v>81</v>
@@ -16684,7 +16734,7 @@
         <v>76</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>75</v>
@@ -16693,11 +16743,11 @@
         <v>75</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>377</v>
+        <v>108</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" t="s" s="2">
-        <v>378</v>
+        <v>109</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -16748,7 +16798,7 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>379</v>
+        <v>110</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -16766,28 +16816,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="144" hidden="true">
+    <row r="144">
       <c r="A144" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E144" t="s" s="2">
-        <v>382</v>
+        <v>112</v>
       </c>
       <c r="F144" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G144" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>75</v>
@@ -16796,11 +16846,11 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>289</v>
+        <v>113</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" t="s" s="2">
-        <v>383</v>
+        <v>138</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -16851,7 +16901,7 @@
         <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>384</v>
+        <v>116</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -16871,17 +16921,17 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>386</v>
+        <v>341</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E145" t="s" s="2">
-        <v>387</v>
+        <v>118</v>
       </c>
       <c r="F145" t="s" s="2">
         <v>81</v>
@@ -16899,11 +16949,11 @@
         <v>75</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>283</v>
+        <v>103</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" t="s" s="2">
-        <v>388</v>
+        <v>119</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -16954,7 +17004,7 @@
         <v>75</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>389</v>
+        <v>120</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -16974,20 +17024,18 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>391</v>
+        <v>351</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E146" t="s" s="2">
-        <v>392</v>
-      </c>
+      <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>76</v>
@@ -17002,12 +17050,10 @@
         <v>75</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>377</v>
+        <v>86</v>
       </c>
       <c r="L146" s="2"/>
-      <c r="M146" t="s" s="2">
-        <v>393</v>
-      </c>
+      <c r="M146" s="2"/>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -17018,7 +17064,7 @@
         <v>75</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>75</v>
+        <v>433</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>75</v>
@@ -17033,13 +17079,11 @@
         <v>75</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y146" s="2"/>
       <c r="Z146" t="s" s="2">
-        <v>75</v>
+        <v>233</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>75</v>
@@ -17057,10 +17101,10 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>394</v>
+        <v>353</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>76</v>
@@ -17080,7 +17124,7 @@
         <v>434</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>396</v>
+        <v>355</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17103,7 +17147,7 @@
         <v>75</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>279</v>
+        <v>86</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
@@ -17114,7 +17158,7 @@
       </c>
       <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
-        <v>75</v>
+        <v>356</v>
       </c>
       <c r="S147" t="s" s="2">
         <v>75</v>
@@ -17132,13 +17176,11 @@
         <v>75</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y147" s="2"/>
       <c r="Z147" t="s" s="2">
-        <v>75</v>
+        <v>357</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>75</v>
@@ -17156,7 +17198,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>397</v>
+        <v>358</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -17174,12 +17216,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
         <v>435</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>399</v>
+        <v>360</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17187,13 +17229,13 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>75</v>
@@ -17202,14 +17244,10 @@
         <v>75</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="L148" s="2"/>
+      <c r="M148" s="2"/>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -17259,10 +17297,10 @@
         <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>402</v>
+        <v>361</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>76</v>
@@ -17277,12 +17315,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="149" hidden="true">
+    <row r="149">
       <c r="A149" t="s" s="2">
         <v>436</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>436</v>
+        <v>363</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17293,10 +17331,10 @@
         <v>81</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>75</v>
@@ -17305,10 +17343,14 @@
         <v>75</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="L149" s="2"/>
-      <c r="M149" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -17358,13 +17400,13 @@
         <v>75</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>436</v>
+        <v>365</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>75</v>
@@ -17378,21 +17420,23 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>438</v>
+        <v>367</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E150" s="2"/>
+      <c r="E150" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>75</v>
@@ -17404,10 +17448,12 @@
         <v>75</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>439</v>
+        <v>86</v>
       </c>
       <c r="L150" s="2"/>
-      <c r="M150" s="2"/>
+      <c r="M150" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -17433,13 +17479,11 @@
         <v>75</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>75</v>
@@ -17457,13 +17501,13 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>438</v>
+        <v>90</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>75</v>
@@ -17477,10 +17521,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>440</v>
+        <v>369</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17491,7 +17535,7 @@
         <v>81</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>75</v>
@@ -17503,10 +17547,12 @@
         <v>75</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>441</v>
+        <v>370</v>
       </c>
       <c r="L151" s="2"/>
-      <c r="M151" s="2"/>
+      <c r="M151" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -17556,13 +17602,13 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>440</v>
+        <v>372</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>75</v>
@@ -17576,10 +17622,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>442</v>
+        <v>374</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17590,10 +17636,10 @@
         <v>81</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>75</v>
@@ -17602,14 +17648,16 @@
         <v>75</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>443</v>
+        <v>86</v>
       </c>
       <c r="L152" s="2"/>
-      <c r="M152" s="2"/>
+      <c r="M152" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
-        <v>75</v>
+        <v>376</v>
       </c>
       <c r="Q152" s="2"/>
       <c r="R152" t="s" s="2">
@@ -17631,35 +17679,35 @@
         <v>75</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>75</v>
+        <v>377</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AC152" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD152" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>442</v>
+        <v>378</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>75</v>
@@ -17671,28 +17719,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="153" hidden="true">
+    <row r="153">
       <c r="A153" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C153" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E153" s="2"/>
+      <c r="E153" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="F153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>75</v>
@@ -17701,12 +17749,12 @@
         <v>75</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M153" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="L153" s="2"/>
+      <c r="M153" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -17756,13 +17804,13 @@
         <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>442</v>
+        <v>384</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>75</v>
@@ -17776,17 +17824,17 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>449</v>
+        <v>386</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>85</v>
+        <v>387</v>
       </c>
       <c r="F154" t="s" s="2">
         <v>81</v>
@@ -17804,11 +17852,11 @@
         <v>75</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>86</v>
+        <v>289</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" t="s" s="2">
-        <v>87</v>
+        <v>388</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -17835,11 +17883,13 @@
         <v>75</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y154" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z154" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>75</v>
@@ -17857,7 +17907,7 @@
         <v>75</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>90</v>
+        <v>389</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -17877,21 +17927,23 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>451</v>
+        <v>391</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E155" s="2"/>
+      <c r="E155" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="F155" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>75</v>
@@ -17903,11 +17955,11 @@
         <v>75</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>92</v>
+        <v>283</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" t="s" s="2">
-        <v>93</v>
+        <v>393</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -17958,13 +18010,13 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>94</v>
+        <v>394</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>75</v>
@@ -17976,18 +18028,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>453</v>
+        <v>396</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E156" s="2"/>
+      <c r="E156" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="F156" t="s" s="2">
         <v>81</v>
       </c>
@@ -17995,7 +18049,7 @@
         <v>76</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>75</v>
@@ -18004,11 +18058,11 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>96</v>
+        <v>382</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" t="s" s="2">
-        <v>97</v>
+        <v>398</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -18059,7 +18113,7 @@
         <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>98</v>
+        <v>399</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -18071,7 +18125,7 @@
         <v>75</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>75</v>
@@ -18079,18 +18133,16 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>455</v>
+        <v>401</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E157" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
         <v>81</v>
       </c>
@@ -18107,12 +18159,10 @@
         <v>75</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>86</v>
+        <v>279</v>
       </c>
       <c r="L157" s="2"/>
-      <c r="M157" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M157" s="2"/>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -18138,11 +18188,13 @@
         <v>75</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y157" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z157" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>75</v>
@@ -18160,7 +18212,7 @@
         <v>75</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>90</v>
+        <v>402</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -18178,28 +18230,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>457</v>
+        <v>404</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E158" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G158" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>75</v>
@@ -18208,11 +18258,13 @@
         <v>75</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L158" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="M158" t="s" s="2">
-        <v>104</v>
+        <v>406</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -18263,10 +18315,10 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>105</v>
+        <v>407</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>76</v>
@@ -18283,23 +18335,21 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E159" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>75</v>
@@ -18311,12 +18361,10 @@
         <v>75</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>108</v>
+        <v>447</v>
       </c>
       <c r="L159" s="2"/>
-      <c r="M159" t="s" s="2">
-        <v>109</v>
-      </c>
+      <c r="M159" s="2"/>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -18366,13 +18414,13 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>110</v>
+        <v>446</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>75</v>
@@ -18386,23 +18434,21 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E160" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>75</v>
@@ -18414,12 +18460,10 @@
         <v>75</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>113</v>
+        <v>449</v>
       </c>
       <c r="L160" s="2"/>
-      <c r="M160" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="M160" s="2"/>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -18427,7 +18471,7 @@
       </c>
       <c r="Q160" s="2"/>
       <c r="R160" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S160" t="s" s="2">
         <v>75</v>
@@ -18469,13 +18513,13 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>116</v>
+        <v>448</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>75</v>
@@ -18489,23 +18533,21 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E161" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>75</v>
@@ -18517,12 +18559,10 @@
         <v>75</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>103</v>
+        <v>451</v>
       </c>
       <c r="L161" s="2"/>
-      <c r="M161" t="s" s="2">
-        <v>119</v>
-      </c>
+      <c r="M161" s="2"/>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -18572,13 +18612,13 @@
         <v>75</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>75</v>
@@ -18592,10 +18632,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18609,7 +18649,7 @@
         <v>82</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>75</v>
@@ -18618,12 +18658,10 @@
         <v>75</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>96</v>
+        <v>453</v>
       </c>
       <c r="L162" s="2"/>
-      <c r="M162" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M162" s="2"/>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -18661,19 +18699,17 @@
         <v>75</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="AC162" s="2"/>
       <c r="AD162" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>126</v>
+        <v>452</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -18693,12 +18729,14 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C163" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C163" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="D163" t="s" s="2">
         <v>75</v>
       </c>
@@ -18707,7 +18745,7 @@
         <v>81</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>75</v>
@@ -18719,21 +18757,23 @@
         <v>75</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L163" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="L163" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
-        <v>468</v>
+        <v>75</v>
       </c>
       <c r="Q163" s="2"/>
       <c r="R163" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S163" t="s" s="2">
-        <v>468</v>
+        <v>75</v>
       </c>
       <c r="T163" t="s" s="2">
         <v>75</v>
@@ -18748,11 +18788,13 @@
         <v>75</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y163" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y163" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z163" t="s" s="2">
-        <v>469</v>
+        <v>75</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>75</v>
@@ -18770,13 +18812,13 @@
         <v>75</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>75</v>
@@ -18790,16 +18832,18 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E164" s="2"/>
+      <c r="E164" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F164" t="s" s="2">
         <v>81</v>
       </c>
@@ -18816,10 +18860,12 @@
         <v>75</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L164" s="2"/>
-      <c r="M164" s="2"/>
+      <c r="M164" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -18827,7 +18873,7 @@
       </c>
       <c r="Q164" s="2"/>
       <c r="R164" t="s" s="2">
-        <v>473</v>
+        <v>75</v>
       </c>
       <c r="S164" t="s" s="2">
         <v>75</v>
@@ -18845,13 +18891,11 @@
         <v>75</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>75</v>
@@ -18869,7 +18913,7 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>474</v>
+        <v>90</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -18889,10 +18933,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18903,7 +18947,7 @@
         <v>81</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>75</v>
@@ -18915,10 +18959,12 @@
         <v>75</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>477</v>
+        <v>92</v>
       </c>
       <c r="L165" s="2"/>
-      <c r="M165" s="2"/>
+      <c r="M165" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -18968,13 +19014,13 @@
         <v>75</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>478</v>
+        <v>94</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>75</v>
@@ -18988,10 +19034,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19014,10 +19060,12 @@
         <v>75</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>477</v>
+        <v>96</v>
       </c>
       <c r="L166" s="2"/>
-      <c r="M166" s="2"/>
+      <c r="M166" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -19067,7 +19115,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>481</v>
+        <v>98</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -19079,7 +19127,7 @@
         <v>75</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>75</v>
@@ -19087,16 +19135,18 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E167" s="2"/>
+      <c r="E167" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F167" t="s" s="2">
         <v>81</v>
       </c>
@@ -19113,10 +19163,12 @@
         <v>75</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>484</v>
+        <v>86</v>
       </c>
       <c r="L167" s="2"/>
-      <c r="M167" s="2"/>
+      <c r="M167" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -19142,13 +19194,11 @@
         <v>75</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y167" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>75</v>
@@ -19166,7 +19216,7 @@
         <v>75</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>485</v>
+        <v>90</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -19186,16 +19236,18 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>486</v>
+        <v>466</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E168" s="2"/>
+      <c r="E168" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F168" t="s" s="2">
         <v>81</v>
       </c>
@@ -19212,10 +19264,12 @@
         <v>75</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>488</v>
+        <v>103</v>
       </c>
       <c r="L168" s="2"/>
-      <c r="M168" s="2"/>
+      <c r="M168" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -19265,7 +19319,7 @@
         <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>489</v>
+        <v>105</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -19285,16 +19339,18 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>490</v>
+        <v>468</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E169" s="2"/>
+      <c r="E169" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F169" t="s" s="2">
         <v>81</v>
       </c>
@@ -19311,10 +19367,12 @@
         <v>75</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>492</v>
+        <v>108</v>
       </c>
       <c r="L169" s="2"/>
-      <c r="M169" s="2"/>
+      <c r="M169" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -19364,7 +19422,7 @@
         <v>75</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>493</v>
+        <v>110</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -19384,18 +19442,20 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E170" s="2"/>
+      <c r="E170" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F170" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G170" t="s" s="2">
         <v>76</v>
@@ -19410,10 +19470,12 @@
         <v>75</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>496</v>
+        <v>113</v>
       </c>
       <c r="L170" s="2"/>
-      <c r="M170" s="2"/>
+      <c r="M170" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -19421,7 +19483,7 @@
       </c>
       <c r="Q170" s="2"/>
       <c r="R170" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S170" t="s" s="2">
         <v>75</v>
@@ -19463,7 +19525,7 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>497</v>
+        <v>116</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -19483,18 +19545,20 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E171" s="2"/>
+      <c r="E171" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="F171" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G171" t="s" s="2">
         <v>76</v>
@@ -19509,10 +19573,12 @@
         <v>75</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>500</v>
+        <v>103</v>
       </c>
       <c r="L171" s="2"/>
-      <c r="M171" s="2"/>
+      <c r="M171" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -19562,7 +19628,7 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>501</v>
+        <v>120</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -19582,10 +19648,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>502</v>
+        <v>474</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19596,7 +19662,7 @@
         <v>81</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>75</v>
@@ -19608,10 +19674,12 @@
         <v>75</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>504</v>
+        <v>96</v>
       </c>
       <c r="L172" s="2"/>
-      <c r="M172" s="2"/>
+      <c r="M172" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -19661,13 +19729,13 @@
         <v>75</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>505</v>
+        <v>126</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>75</v>
@@ -19681,10 +19749,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>506</v>
+        <v>476</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>507</v>
+        <v>477</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19707,21 +19775,21 @@
         <v>75</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>508</v>
+        <v>86</v>
       </c>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
-        <v>75</v>
+        <v>478</v>
       </c>
       <c r="Q173" s="2"/>
       <c r="R173" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S173" t="s" s="2">
-        <v>75</v>
+        <v>478</v>
       </c>
       <c r="T173" t="s" s="2">
         <v>75</v>
@@ -19736,13 +19804,11 @@
         <v>75</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y173" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y173" s="2"/>
       <c r="Z173" t="s" s="2">
-        <v>75</v>
+        <v>479</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>75</v>
@@ -19760,7 +19826,7 @@
         <v>75</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>509</v>
+        <v>480</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -19780,10 +19846,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19806,7 +19872,7 @@
         <v>75</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>512</v>
+        <v>108</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -19817,7 +19883,7 @@
       </c>
       <c r="Q174" s="2"/>
       <c r="R174" t="s" s="2">
-        <v>75</v>
+        <v>483</v>
       </c>
       <c r="S174" t="s" s="2">
         <v>75</v>
@@ -19859,7 +19925,7 @@
         <v>75</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -19879,10 +19945,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>514</v>
+        <v>485</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>515</v>
+        <v>486</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19905,7 +19971,7 @@
         <v>75</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
@@ -19958,7 +20024,7 @@
         <v>75</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>517</v>
+        <v>488</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -19978,10 +20044,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20004,7 +20070,7 @@
         <v>75</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
@@ -20057,7 +20123,7 @@
         <v>75</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>521</v>
+        <v>491</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -20077,14 +20143,12 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>522</v>
+        <v>492</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C177" t="s" s="2">
-        <v>523</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
         <v>75</v>
       </c>
@@ -20093,7 +20157,7 @@
         <v>81</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>75</v>
@@ -20105,11 +20169,9 @@
         <v>75</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="L177" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="L177" s="2"/>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -20160,13 +20222,13 @@
         <v>75</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>442</v>
+        <v>495</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>75</v>
@@ -20180,18 +20242,16 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>525</v>
+        <v>496</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>449</v>
+        <v>497</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E178" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
         <v>81</v>
       </c>
@@ -20208,12 +20268,10 @@
         <v>75</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>86</v>
+        <v>498</v>
       </c>
       <c r="L178" s="2"/>
-      <c r="M178" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M178" s="2"/>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -20239,11 +20297,13 @@
         <v>75</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y178" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z178" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>75</v>
@@ -20261,7 +20321,7 @@
         <v>75</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>90</v>
+        <v>499</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -20281,10 +20341,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>526</v>
+        <v>500</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>451</v>
+        <v>501</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20295,7 +20355,7 @@
         <v>81</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>75</v>
@@ -20307,12 +20367,10 @@
         <v>75</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>92</v>
+        <v>502</v>
       </c>
       <c r="L179" s="2"/>
-      <c r="M179" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M179" s="2"/>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -20362,13 +20420,13 @@
         <v>75</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>94</v>
+        <v>503</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>75</v>
@@ -20382,10 +20440,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20408,12 +20466,10 @@
         <v>75</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>96</v>
+        <v>506</v>
       </c>
       <c r="L180" s="2"/>
-      <c r="M180" t="s" s="2">
-        <v>97</v>
-      </c>
+      <c r="M180" s="2"/>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -20463,7 +20519,7 @@
         <v>75</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>98</v>
+        <v>507</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -20475,7 +20531,7 @@
         <v>75</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>75</v>
@@ -20483,18 +20539,16 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E181" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
         <v>81</v>
       </c>
@@ -20511,12 +20565,10 @@
         <v>75</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>86</v>
+        <v>510</v>
       </c>
       <c r="L181" s="2"/>
-      <c r="M181" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M181" s="2"/>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -20542,11 +20594,13 @@
         <v>75</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y181" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y181" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z181" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>75</v>
@@ -20564,7 +20618,7 @@
         <v>75</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>90</v>
+        <v>511</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -20584,18 +20638,16 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E182" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
         <v>81</v>
       </c>
@@ -20612,12 +20664,10 @@
         <v>75</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>103</v>
+        <v>514</v>
       </c>
       <c r="L182" s="2"/>
-      <c r="M182" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="M182" s="2"/>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -20667,7 +20717,7 @@
         <v>75</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>105</v>
+        <v>515</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -20687,18 +20737,16 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>459</v>
+        <v>517</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E183" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>81</v>
       </c>
@@ -20715,12 +20763,10 @@
         <v>75</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>108</v>
+        <v>518</v>
       </c>
       <c r="L183" s="2"/>
-      <c r="M183" t="s" s="2">
-        <v>109</v>
-      </c>
+      <c r="M183" s="2"/>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -20770,7 +20816,7 @@
         <v>75</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>110</v>
+        <v>519</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -20790,20 +20836,18 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>461</v>
+        <v>521</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E184" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G184" t="s" s="2">
         <v>76</v>
@@ -20818,12 +20862,10 @@
         <v>75</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>113</v>
+        <v>522</v>
       </c>
       <c r="L184" s="2"/>
-      <c r="M184" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="M184" s="2"/>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -20831,7 +20873,7 @@
       </c>
       <c r="Q184" s="2"/>
       <c r="R184" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S184" t="s" s="2">
         <v>75</v>
@@ -20873,7 +20915,7 @@
         <v>75</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>116</v>
+        <v>523</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -20893,20 +20935,18 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>463</v>
+        <v>525</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E185" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G185" t="s" s="2">
         <v>76</v>
@@ -20921,12 +20961,10 @@
         <v>75</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>103</v>
+        <v>526</v>
       </c>
       <c r="L185" s="2"/>
-      <c r="M185" t="s" s="2">
-        <v>119</v>
-      </c>
+      <c r="M185" s="2"/>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -20976,7 +21014,7 @@
         <v>75</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>120</v>
+        <v>527</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -20996,10 +21034,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>465</v>
+        <v>529</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21010,7 +21048,7 @@
         <v>81</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>75</v>
@@ -21022,12 +21060,10 @@
         <v>75</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>96</v>
+        <v>530</v>
       </c>
       <c r="L186" s="2"/>
-      <c r="M186" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M186" s="2"/>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -21077,13 +21113,13 @@
         <v>75</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>126</v>
+        <v>531</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>75</v>
@@ -21097,12 +21133,14 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C187" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C187" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="D187" t="s" s="2">
         <v>75</v>
       </c>
@@ -21111,7 +21149,7 @@
         <v>81</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>75</v>
@@ -21123,21 +21161,23 @@
         <v>75</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L187" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="L187" t="s" s="2">
+        <v>534</v>
+      </c>
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
-        <v>468</v>
+        <v>75</v>
       </c>
       <c r="Q187" s="2"/>
       <c r="R187" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S187" t="s" s="2">
-        <v>468</v>
+        <v>75</v>
       </c>
       <c r="T187" t="s" s="2">
         <v>75</v>
@@ -21152,11 +21192,13 @@
         <v>75</v>
       </c>
       <c r="X187" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y187" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z187" t="s" s="2">
-        <v>469</v>
+        <v>75</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>75</v>
@@ -21174,13 +21216,13 @@
         <v>75</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH187" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI187" t="s" s="2">
         <v>75</v>
@@ -21197,13 +21239,15 @@
         <v>535</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E188" s="2"/>
+      <c r="E188" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F188" t="s" s="2">
         <v>81</v>
       </c>
@@ -21220,10 +21264,12 @@
         <v>75</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L188" s="2"/>
-      <c r="M188" s="2"/>
+      <c r="M188" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -21231,7 +21277,7 @@
       </c>
       <c r="Q188" s="2"/>
       <c r="R188" t="s" s="2">
-        <v>473</v>
+        <v>75</v>
       </c>
       <c r="S188" t="s" s="2">
         <v>75</v>
@@ -21249,13 +21295,11 @@
         <v>75</v>
       </c>
       <c r="X188" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>75</v>
@@ -21273,7 +21317,7 @@
         <v>75</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>474</v>
+        <v>90</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -21296,7 +21340,7 @@
         <v>536</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21307,7 +21351,7 @@
         <v>81</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H189" t="s" s="2">
         <v>75</v>
@@ -21319,10 +21363,12 @@
         <v>75</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>477</v>
+        <v>92</v>
       </c>
       <c r="L189" s="2"/>
-      <c r="M189" s="2"/>
+      <c r="M189" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -21372,13 +21418,13 @@
         <v>75</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>478</v>
+        <v>94</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI189" t="s" s="2">
         <v>75</v>
@@ -21395,7 +21441,7 @@
         <v>537</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21418,10 +21464,12 @@
         <v>75</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>477</v>
+        <v>96</v>
       </c>
       <c r="L190" s="2"/>
-      <c r="M190" s="2"/>
+      <c r="M190" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
@@ -21471,7 +21519,7 @@
         <v>75</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>481</v>
+        <v>98</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
@@ -21483,7 +21531,7 @@
         <v>75</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>75</v>
@@ -21494,13 +21542,15 @@
         <v>538</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E191" s="2"/>
+      <c r="E191" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F191" t="s" s="2">
         <v>81</v>
       </c>
@@ -21517,10 +21567,12 @@
         <v>75</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>484</v>
+        <v>86</v>
       </c>
       <c r="L191" s="2"/>
-      <c r="M191" s="2"/>
+      <c r="M191" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
@@ -21546,13 +21598,11 @@
         <v>75</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>75</v>
@@ -21570,7 +21620,7 @@
         <v>75</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>485</v>
+        <v>90</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -21593,13 +21643,15 @@
         <v>539</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E192" s="2"/>
+      <c r="E192" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F192" t="s" s="2">
         <v>81</v>
       </c>
@@ -21616,10 +21668,12 @@
         <v>75</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>488</v>
+        <v>103</v>
       </c>
       <c r="L192" s="2"/>
-      <c r="M192" s="2"/>
+      <c r="M192" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
@@ -21669,7 +21723,7 @@
         <v>75</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>489</v>
+        <v>105</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -21692,13 +21746,15 @@
         <v>540</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E193" s="2"/>
+      <c r="E193" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F193" t="s" s="2">
         <v>81</v>
       </c>
@@ -21715,10 +21771,12 @@
         <v>75</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>492</v>
+        <v>108</v>
       </c>
       <c r="L193" s="2"/>
-      <c r="M193" s="2"/>
+      <c r="M193" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -21768,7 +21826,7 @@
         <v>75</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>493</v>
+        <v>110</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -21791,15 +21849,17 @@
         <v>541</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E194" s="2"/>
+      <c r="E194" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F194" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G194" t="s" s="2">
         <v>76</v>
@@ -21814,10 +21874,12 @@
         <v>75</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>542</v>
+        <v>113</v>
       </c>
       <c r="L194" s="2"/>
-      <c r="M194" s="2"/>
+      <c r="M194" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -21825,7 +21887,7 @@
       </c>
       <c r="Q194" s="2"/>
       <c r="R194" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S194" t="s" s="2">
         <v>75</v>
@@ -21867,7 +21929,7 @@
         <v>75</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>497</v>
+        <v>116</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -21887,18 +21949,20 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E195" s="2"/>
+      <c r="E195" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="F195" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G195" t="s" s="2">
         <v>76</v>
@@ -21913,10 +21977,12 @@
         <v>75</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>500</v>
+        <v>103</v>
       </c>
       <c r="L195" s="2"/>
-      <c r="M195" s="2"/>
+      <c r="M195" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -21966,7 +22032,7 @@
         <v>75</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>501</v>
+        <v>120</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -21986,10 +22052,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22000,7 +22066,7 @@
         <v>81</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>75</v>
@@ -22012,10 +22078,12 @@
         <v>75</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>545</v>
+        <v>96</v>
       </c>
       <c r="L196" s="2"/>
-      <c r="M196" s="2"/>
+      <c r="M196" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -22065,13 +22133,13 @@
         <v>75</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>505</v>
+        <v>126</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>75</v>
@@ -22085,10 +22153,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>507</v>
+        <v>477</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22111,21 +22179,21 @@
         <v>75</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>508</v>
+        <v>86</v>
       </c>
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
-        <v>75</v>
+        <v>478</v>
       </c>
       <c r="Q197" s="2"/>
       <c r="R197" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S197" t="s" s="2">
-        <v>75</v>
+        <v>478</v>
       </c>
       <c r="T197" t="s" s="2">
         <v>75</v>
@@ -22140,13 +22208,11 @@
         <v>75</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y197" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y197" s="2"/>
       <c r="Z197" t="s" s="2">
-        <v>75</v>
+        <v>479</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>75</v>
@@ -22164,7 +22230,7 @@
         <v>75</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>509</v>
+        <v>480</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
@@ -22184,10 +22250,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22210,7 +22276,7 @@
         <v>75</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>512</v>
+        <v>108</v>
       </c>
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
@@ -22221,7 +22287,7 @@
       </c>
       <c r="Q198" s="2"/>
       <c r="R198" t="s" s="2">
-        <v>75</v>
+        <v>483</v>
       </c>
       <c r="S198" t="s" s="2">
         <v>75</v>
@@ -22263,7 +22329,7 @@
         <v>75</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
@@ -22283,10 +22349,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>515</v>
+        <v>486</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22309,7 +22375,7 @@
         <v>75</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
@@ -22362,7 +22428,7 @@
         <v>75</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>517</v>
+        <v>488</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -22382,10 +22448,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22408,7 +22474,7 @@
         <v>75</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
@@ -22461,7 +22527,7 @@
         <v>75</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>521</v>
+        <v>491</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
@@ -22481,14 +22547,12 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C201" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
         <v>75</v>
       </c>
@@ -22497,7 +22561,7 @@
         <v>81</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H201" t="s" s="2">
         <v>75</v>
@@ -22509,11 +22573,9 @@
         <v>75</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="L201" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="L201" s="2"/>
       <c r="M201" s="2"/>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -22564,13 +22626,13 @@
         <v>75</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>442</v>
+        <v>495</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI201" t="s" s="2">
         <v>75</v>
@@ -22584,18 +22646,16 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>449</v>
+        <v>497</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E202" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E202" s="2"/>
       <c r="F202" t="s" s="2">
         <v>81</v>
       </c>
@@ -22612,12 +22672,10 @@
         <v>75</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>86</v>
+        <v>498</v>
       </c>
       <c r="L202" s="2"/>
-      <c r="M202" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M202" s="2"/>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
@@ -22643,11 +22701,13 @@
         <v>75</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y202" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y202" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z202" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>75</v>
@@ -22665,7 +22725,7 @@
         <v>75</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>90</v>
+        <v>499</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -22685,10 +22745,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>451</v>
+        <v>501</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22699,7 +22759,7 @@
         <v>81</v>
       </c>
       <c r="G203" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H203" t="s" s="2">
         <v>75</v>
@@ -22711,12 +22771,10 @@
         <v>75</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>92</v>
+        <v>502</v>
       </c>
       <c r="L203" s="2"/>
-      <c r="M203" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M203" s="2"/>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
@@ -22766,13 +22824,13 @@
         <v>75</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>94</v>
+        <v>503</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH203" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI203" t="s" s="2">
         <v>75</v>
@@ -22786,10 +22844,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22812,12 +22870,10 @@
         <v>75</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>96</v>
+        <v>552</v>
       </c>
       <c r="L204" s="2"/>
-      <c r="M204" t="s" s="2">
-        <v>97</v>
-      </c>
+      <c r="M204" s="2"/>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -22867,7 +22923,7 @@
         <v>75</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>98</v>
+        <v>507</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -22879,7 +22935,7 @@
         <v>75</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>75</v>
@@ -22887,18 +22943,16 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E205" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
         <v>81</v>
       </c>
@@ -22915,12 +22969,10 @@
         <v>75</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>86</v>
+        <v>510</v>
       </c>
       <c r="L205" s="2"/>
-      <c r="M205" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M205" s="2"/>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -22946,11 +22998,13 @@
         <v>75</v>
       </c>
       <c r="X205" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y205" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y205" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z205" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA205" t="s" s="2">
         <v>75</v>
@@ -22968,7 +23022,7 @@
         <v>75</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>90</v>
+        <v>511</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -22988,18 +23042,16 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E206" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="E206" s="2"/>
       <c r="F206" t="s" s="2">
         <v>81</v>
       </c>
@@ -23016,12 +23068,10 @@
         <v>75</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>103</v>
+        <v>555</v>
       </c>
       <c r="L206" s="2"/>
-      <c r="M206" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="M206" s="2"/>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -23071,7 +23121,7 @@
         <v>75</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>105</v>
+        <v>515</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -23091,18 +23141,16 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>459</v>
+        <v>517</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E207" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
         <v>81</v>
       </c>
@@ -23119,12 +23167,10 @@
         <v>75</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>108</v>
+        <v>518</v>
       </c>
       <c r="L207" s="2"/>
-      <c r="M207" t="s" s="2">
-        <v>109</v>
-      </c>
+      <c r="M207" s="2"/>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -23174,7 +23220,7 @@
         <v>75</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>110</v>
+        <v>519</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -23194,20 +23240,18 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>461</v>
+        <v>521</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E208" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G208" t="s" s="2">
         <v>76</v>
@@ -23222,12 +23266,10 @@
         <v>75</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>113</v>
+        <v>522</v>
       </c>
       <c r="L208" s="2"/>
-      <c r="M208" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="M208" s="2"/>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -23235,7 +23277,7 @@
       </c>
       <c r="Q208" s="2"/>
       <c r="R208" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S208" t="s" s="2">
         <v>75</v>
@@ -23277,7 +23319,7 @@
         <v>75</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>116</v>
+        <v>523</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -23297,20 +23339,18 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>463</v>
+        <v>525</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E209" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G209" t="s" s="2">
         <v>76</v>
@@ -23325,12 +23365,10 @@
         <v>75</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>103</v>
+        <v>526</v>
       </c>
       <c r="L209" s="2"/>
-      <c r="M209" t="s" s="2">
-        <v>119</v>
-      </c>
+      <c r="M209" s="2"/>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
@@ -23380,7 +23418,7 @@
         <v>75</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>120</v>
+        <v>527</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -23400,10 +23438,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>465</v>
+        <v>529</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23414,7 +23452,7 @@
         <v>81</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H210" t="s" s="2">
         <v>75</v>
@@ -23426,12 +23464,10 @@
         <v>75</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>96</v>
+        <v>530</v>
       </c>
       <c r="L210" s="2"/>
-      <c r="M210" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M210" s="2"/>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -23481,13 +23517,13 @@
         <v>75</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>126</v>
+        <v>531</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>75</v>
@@ -23501,12 +23537,14 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C211" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C211" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="D211" t="s" s="2">
         <v>75</v>
       </c>
@@ -23515,7 +23553,7 @@
         <v>81</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>75</v>
@@ -23527,21 +23565,23 @@
         <v>75</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L211" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="L211" t="s" s="2">
+        <v>562</v>
+      </c>
       <c r="M211" s="2"/>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
-        <v>468</v>
+        <v>75</v>
       </c>
       <c r="Q211" s="2"/>
       <c r="R211" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S211" t="s" s="2">
-        <v>468</v>
+        <v>75</v>
       </c>
       <c r="T211" t="s" s="2">
         <v>75</v>
@@ -23556,11 +23596,13 @@
         <v>75</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y211" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y211" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z211" t="s" s="2">
-        <v>469</v>
+        <v>75</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>75</v>
@@ -23578,13 +23620,13 @@
         <v>75</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>75</v>
@@ -23601,13 +23643,15 @@
         <v>563</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E212" s="2"/>
+      <c r="E212" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F212" t="s" s="2">
         <v>81</v>
       </c>
@@ -23624,10 +23668,12 @@
         <v>75</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L212" s="2"/>
-      <c r="M212" s="2"/>
+      <c r="M212" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -23635,7 +23681,7 @@
       </c>
       <c r="Q212" s="2"/>
       <c r="R212" t="s" s="2">
-        <v>473</v>
+        <v>75</v>
       </c>
       <c r="S212" t="s" s="2">
         <v>75</v>
@@ -23653,13 +23699,11 @@
         <v>75</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y212" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y212" s="2"/>
       <c r="Z212" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>75</v>
@@ -23677,7 +23721,7 @@
         <v>75</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>474</v>
+        <v>90</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
@@ -23700,7 +23744,7 @@
         <v>564</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23711,7 +23755,7 @@
         <v>81</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>75</v>
@@ -23723,10 +23767,12 @@
         <v>75</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>477</v>
+        <v>92</v>
       </c>
       <c r="L213" s="2"/>
-      <c r="M213" s="2"/>
+      <c r="M213" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -23776,13 +23822,13 @@
         <v>75</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>478</v>
+        <v>94</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI213" t="s" s="2">
         <v>75</v>
@@ -23799,7 +23845,7 @@
         <v>565</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23822,10 +23868,12 @@
         <v>75</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>477</v>
+        <v>96</v>
       </c>
       <c r="L214" s="2"/>
-      <c r="M214" s="2"/>
+      <c r="M214" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
@@ -23875,7 +23923,7 @@
         <v>75</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>481</v>
+        <v>98</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -23887,7 +23935,7 @@
         <v>75</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK214" t="s" s="2">
         <v>75</v>
@@ -23898,13 +23946,15 @@
         <v>566</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E215" s="2"/>
+      <c r="E215" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F215" t="s" s="2">
         <v>81</v>
       </c>
@@ -23921,10 +23971,12 @@
         <v>75</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>484</v>
+        <v>86</v>
       </c>
       <c r="L215" s="2"/>
-      <c r="M215" s="2"/>
+      <c r="M215" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -23950,13 +24002,11 @@
         <v>75</v>
       </c>
       <c r="X215" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y215" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>75</v>
@@ -23974,7 +24024,7 @@
         <v>75</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>485</v>
+        <v>90</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
@@ -23997,13 +24047,15 @@
         <v>567</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E216" s="2"/>
+      <c r="E216" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F216" t="s" s="2">
         <v>81</v>
       </c>
@@ -24020,10 +24072,12 @@
         <v>75</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>488</v>
+        <v>103</v>
       </c>
       <c r="L216" s="2"/>
-      <c r="M216" s="2"/>
+      <c r="M216" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -24073,7 +24127,7 @@
         <v>75</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>489</v>
+        <v>105</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -24096,13 +24150,15 @@
         <v>568</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E217" s="2"/>
+      <c r="E217" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F217" t="s" s="2">
         <v>81</v>
       </c>
@@ -24119,10 +24175,12 @@
         <v>75</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>492</v>
+        <v>108</v>
       </c>
       <c r="L217" s="2"/>
-      <c r="M217" s="2"/>
+      <c r="M217" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
@@ -24172,7 +24230,7 @@
         <v>75</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>493</v>
+        <v>110</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -24195,15 +24253,17 @@
         <v>569</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E218" s="2"/>
+      <c r="E218" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F218" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G218" t="s" s="2">
         <v>76</v>
@@ -24218,10 +24278,12 @@
         <v>75</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>496</v>
+        <v>113</v>
       </c>
       <c r="L218" s="2"/>
-      <c r="M218" s="2"/>
+      <c r="M218" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
@@ -24229,7 +24291,7 @@
       </c>
       <c r="Q218" s="2"/>
       <c r="R218" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S218" t="s" s="2">
         <v>75</v>
@@ -24271,7 +24333,7 @@
         <v>75</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>497</v>
+        <v>116</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -24294,15 +24356,17 @@
         <v>570</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E219" s="2"/>
+      <c r="E219" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="F219" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G219" t="s" s="2">
         <v>76</v>
@@ -24317,10 +24381,12 @@
         <v>75</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>571</v>
+        <v>103</v>
       </c>
       <c r="L219" s="2"/>
-      <c r="M219" s="2"/>
+      <c r="M219" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
@@ -24370,7 +24436,7 @@
         <v>75</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>501</v>
+        <v>120</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -24390,10 +24456,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24404,7 +24470,7 @@
         <v>81</v>
       </c>
       <c r="G220" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H220" t="s" s="2">
         <v>75</v>
@@ -24416,10 +24482,12 @@
         <v>75</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>545</v>
+        <v>96</v>
       </c>
       <c r="L220" s="2"/>
-      <c r="M220" s="2"/>
+      <c r="M220" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
@@ -24469,13 +24537,13 @@
         <v>75</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>505</v>
+        <v>126</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI220" t="s" s="2">
         <v>75</v>
@@ -24489,10 +24557,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>507</v>
+        <v>477</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24515,21 +24583,21 @@
         <v>75</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>508</v>
+        <v>86</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
-        <v>75</v>
+        <v>478</v>
       </c>
       <c r="Q221" s="2"/>
       <c r="R221" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S221" t="s" s="2">
-        <v>75</v>
+        <v>478</v>
       </c>
       <c r="T221" t="s" s="2">
         <v>75</v>
@@ -24544,13 +24612,11 @@
         <v>75</v>
       </c>
       <c r="X221" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y221" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y221" s="2"/>
       <c r="Z221" t="s" s="2">
-        <v>75</v>
+        <v>479</v>
       </c>
       <c r="AA221" t="s" s="2">
         <v>75</v>
@@ -24568,7 +24634,7 @@
         <v>75</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>509</v>
+        <v>480</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
@@ -24588,10 +24654,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24614,7 +24680,7 @@
         <v>75</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>512</v>
+        <v>108</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -24625,7 +24691,7 @@
       </c>
       <c r="Q222" s="2"/>
       <c r="R222" t="s" s="2">
-        <v>75</v>
+        <v>483</v>
       </c>
       <c r="S222" t="s" s="2">
         <v>75</v>
@@ -24667,7 +24733,7 @@
         <v>75</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -24687,10 +24753,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>515</v>
+        <v>486</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24713,7 +24779,7 @@
         <v>75</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -24766,7 +24832,7 @@
         <v>75</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>517</v>
+        <v>488</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -24786,10 +24852,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24812,7 +24878,7 @@
         <v>75</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
@@ -24865,7 +24931,7 @@
         <v>75</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>521</v>
+        <v>491</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -24885,14 +24951,12 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C225" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
         <v>75</v>
       </c>
@@ -24901,7 +24965,7 @@
         <v>81</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>75</v>
@@ -24913,11 +24977,9 @@
         <v>75</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="L225" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="L225" s="2"/>
       <c r="M225" s="2"/>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -24968,13 +25030,13 @@
         <v>75</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>442</v>
+        <v>495</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH225" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI225" t="s" s="2">
         <v>75</v>
@@ -24988,18 +25050,16 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>449</v>
+        <v>497</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E226" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E226" s="2"/>
       <c r="F226" t="s" s="2">
         <v>81</v>
       </c>
@@ -25016,12 +25076,10 @@
         <v>75</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>86</v>
+        <v>498</v>
       </c>
       <c r="L226" s="2"/>
-      <c r="M226" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M226" s="2"/>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
@@ -25047,11 +25105,13 @@
         <v>75</v>
       </c>
       <c r="X226" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y226" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y226" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z226" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>75</v>
@@ -25069,7 +25129,7 @@
         <v>75</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>90</v>
+        <v>499</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -25089,10 +25149,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>451</v>
+        <v>501</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25103,7 +25163,7 @@
         <v>81</v>
       </c>
       <c r="G227" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H227" t="s" s="2">
         <v>75</v>
@@ -25115,12 +25175,10 @@
         <v>75</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>92</v>
+        <v>502</v>
       </c>
       <c r="L227" s="2"/>
-      <c r="M227" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M227" s="2"/>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
@@ -25170,13 +25228,13 @@
         <v>75</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>94</v>
+        <v>503</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH227" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI227" t="s" s="2">
         <v>75</v>
@@ -25190,10 +25248,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25216,12 +25274,10 @@
         <v>75</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>96</v>
+        <v>506</v>
       </c>
       <c r="L228" s="2"/>
-      <c r="M228" t="s" s="2">
-        <v>97</v>
-      </c>
+      <c r="M228" s="2"/>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
@@ -25271,7 +25327,7 @@
         <v>75</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>98</v>
+        <v>507</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
@@ -25283,7 +25339,7 @@
         <v>75</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK228" t="s" s="2">
         <v>75</v>
@@ -25291,18 +25347,16 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E229" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
         <v>81</v>
       </c>
@@ -25319,12 +25373,10 @@
         <v>75</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>86</v>
+        <v>581</v>
       </c>
       <c r="L229" s="2"/>
-      <c r="M229" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M229" s="2"/>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
       <c r="P229" t="s" s="2">
@@ -25350,11 +25402,13 @@
         <v>75</v>
       </c>
       <c r="X229" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y229" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y229" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z229" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>75</v>
@@ -25372,7 +25426,7 @@
         <v>75</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>90</v>
+        <v>511</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -25392,18 +25446,16 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E230" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
         <v>81</v>
       </c>
@@ -25420,12 +25472,10 @@
         <v>75</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>103</v>
+        <v>555</v>
       </c>
       <c r="L230" s="2"/>
-      <c r="M230" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="M230" s="2"/>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
@@ -25475,7 +25525,7 @@
         <v>75</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>105</v>
+        <v>515</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
@@ -25495,18 +25545,16 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>459</v>
+        <v>517</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E231" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
         <v>81</v>
       </c>
@@ -25523,12 +25571,10 @@
         <v>75</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>108</v>
+        <v>518</v>
       </c>
       <c r="L231" s="2"/>
-      <c r="M231" t="s" s="2">
-        <v>109</v>
-      </c>
+      <c r="M231" s="2"/>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
@@ -25578,7 +25624,7 @@
         <v>75</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>110</v>
+        <v>519</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
@@ -25598,20 +25644,18 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>461</v>
+        <v>521</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E232" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E232" s="2"/>
       <c r="F232" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G232" t="s" s="2">
         <v>76</v>
@@ -25626,12 +25670,10 @@
         <v>75</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>113</v>
+        <v>522</v>
       </c>
       <c r="L232" s="2"/>
-      <c r="M232" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="M232" s="2"/>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -25639,7 +25681,7 @@
       </c>
       <c r="Q232" s="2"/>
       <c r="R232" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S232" t="s" s="2">
         <v>75</v>
@@ -25681,7 +25723,7 @@
         <v>75</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>116</v>
+        <v>523</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -25701,20 +25743,18 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>463</v>
+        <v>525</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E233" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E233" s="2"/>
       <c r="F233" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G233" t="s" s="2">
         <v>76</v>
@@ -25729,12 +25769,10 @@
         <v>75</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>103</v>
+        <v>526</v>
       </c>
       <c r="L233" s="2"/>
-      <c r="M233" t="s" s="2">
-        <v>119</v>
-      </c>
+      <c r="M233" s="2"/>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
@@ -25784,7 +25822,7 @@
         <v>75</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>120</v>
+        <v>527</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
@@ -25804,10 +25842,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>465</v>
+        <v>529</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -25818,7 +25856,7 @@
         <v>81</v>
       </c>
       <c r="G234" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H234" t="s" s="2">
         <v>75</v>
@@ -25830,12 +25868,10 @@
         <v>75</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>96</v>
+        <v>530</v>
       </c>
       <c r="L234" s="2"/>
-      <c r="M234" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M234" s="2"/>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
       <c r="P234" t="s" s="2">
@@ -25885,13 +25921,13 @@
         <v>75</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>126</v>
+        <v>531</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH234" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI234" t="s" s="2">
         <v>75</v>
@@ -25905,12 +25941,14 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C235" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C235" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="D235" t="s" s="2">
         <v>75</v>
       </c>
@@ -25919,7 +25957,7 @@
         <v>81</v>
       </c>
       <c r="G235" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H235" t="s" s="2">
         <v>75</v>
@@ -25931,21 +25969,23 @@
         <v>75</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L235" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="L235" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="M235" s="2"/>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
-        <v>468</v>
+        <v>75</v>
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S235" t="s" s="2">
-        <v>468</v>
+        <v>75</v>
       </c>
       <c r="T235" t="s" s="2">
         <v>75</v>
@@ -25960,11 +26000,13 @@
         <v>75</v>
       </c>
       <c r="X235" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y235" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y235" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z235" t="s" s="2">
-        <v>469</v>
+        <v>75</v>
       </c>
       <c r="AA235" t="s" s="2">
         <v>75</v>
@@ -25982,13 +26024,13 @@
         <v>75</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH235" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI235" t="s" s="2">
         <v>75</v>
@@ -26005,13 +26047,15 @@
         <v>590</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E236" s="2"/>
+      <c r="E236" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F236" t="s" s="2">
         <v>81</v>
       </c>
@@ -26028,10 +26072,12 @@
         <v>75</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L236" s="2"/>
-      <c r="M236" s="2"/>
+      <c r="M236" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
@@ -26039,7 +26085,7 @@
       </c>
       <c r="Q236" s="2"/>
       <c r="R236" t="s" s="2">
-        <v>473</v>
+        <v>75</v>
       </c>
       <c r="S236" t="s" s="2">
         <v>75</v>
@@ -26057,13 +26103,11 @@
         <v>75</v>
       </c>
       <c r="X236" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y236" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y236" s="2"/>
       <c r="Z236" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>75</v>
@@ -26081,7 +26125,7 @@
         <v>75</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>474</v>
+        <v>90</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>81</v>
@@ -26104,7 +26148,7 @@
         <v>591</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26115,7 +26159,7 @@
         <v>81</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>75</v>
@@ -26127,10 +26171,12 @@
         <v>75</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>477</v>
+        <v>92</v>
       </c>
       <c r="L237" s="2"/>
-      <c r="M237" s="2"/>
+      <c r="M237" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
       <c r="P237" t="s" s="2">
@@ -26180,13 +26226,13 @@
         <v>75</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>478</v>
+        <v>94</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI237" t="s" s="2">
         <v>75</v>
@@ -26203,7 +26249,7 @@
         <v>592</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26226,10 +26272,12 @@
         <v>75</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>477</v>
+        <v>96</v>
       </c>
       <c r="L238" s="2"/>
-      <c r="M238" s="2"/>
+      <c r="M238" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
       <c r="P238" t="s" s="2">
@@ -26279,7 +26327,7 @@
         <v>75</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>481</v>
+        <v>98</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>81</v>
@@ -26291,7 +26339,7 @@
         <v>75</v>
       </c>
       <c r="AJ238" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK238" t="s" s="2">
         <v>75</v>
@@ -26302,13 +26350,15 @@
         <v>593</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E239" s="2"/>
+      <c r="E239" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F239" t="s" s="2">
         <v>81</v>
       </c>
@@ -26325,10 +26375,12 @@
         <v>75</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>484</v>
+        <v>86</v>
       </c>
       <c r="L239" s="2"/>
-      <c r="M239" s="2"/>
+      <c r="M239" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
@@ -26354,13 +26406,11 @@
         <v>75</v>
       </c>
       <c r="X239" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y239" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y239" s="2"/>
       <c r="Z239" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>75</v>
@@ -26378,7 +26428,7 @@
         <v>75</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>485</v>
+        <v>90</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>81</v>
@@ -26401,13 +26451,15 @@
         <v>594</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E240" s="2"/>
+      <c r="E240" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F240" t="s" s="2">
         <v>81</v>
       </c>
@@ -26424,10 +26476,12 @@
         <v>75</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>595</v>
+        <v>103</v>
       </c>
       <c r="L240" s="2"/>
-      <c r="M240" s="2"/>
+      <c r="M240" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N240" s="2"/>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
@@ -26477,7 +26531,7 @@
         <v>75</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>489</v>
+        <v>105</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>81</v>
@@ -26497,16 +26551,18 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E241" s="2"/>
+      <c r="E241" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F241" t="s" s="2">
         <v>81</v>
       </c>
@@ -26523,10 +26579,12 @@
         <v>75</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>492</v>
+        <v>108</v>
       </c>
       <c r="L241" s="2"/>
-      <c r="M241" s="2"/>
+      <c r="M241" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
@@ -26576,7 +26634,7 @@
         <v>75</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>493</v>
+        <v>110</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>81</v>
@@ -26596,18 +26654,20 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E242" s="2"/>
+      <c r="E242" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F242" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G242" t="s" s="2">
         <v>76</v>
@@ -26622,10 +26682,12 @@
         <v>75</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>496</v>
+        <v>113</v>
       </c>
       <c r="L242" s="2"/>
-      <c r="M242" s="2"/>
+      <c r="M242" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
       <c r="P242" t="s" s="2">
@@ -26633,7 +26695,7 @@
       </c>
       <c r="Q242" s="2"/>
       <c r="R242" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S242" t="s" s="2">
         <v>75</v>
@@ -26675,7 +26737,7 @@
         <v>75</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>497</v>
+        <v>116</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
@@ -26695,18 +26757,20 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E243" s="2"/>
+      <c r="E243" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="F243" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G243" t="s" s="2">
         <v>76</v>
@@ -26721,10 +26785,12 @@
         <v>75</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>500</v>
+        <v>103</v>
       </c>
       <c r="L243" s="2"/>
-      <c r="M243" s="2"/>
+      <c r="M243" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="N243" s="2"/>
       <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
@@ -26774,7 +26840,7 @@
         <v>75</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>501</v>
+        <v>120</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>81</v>
@@ -26794,10 +26860,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -26808,7 +26874,7 @@
         <v>81</v>
       </c>
       <c r="G244" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H244" t="s" s="2">
         <v>75</v>
@@ -26820,10 +26886,12 @@
         <v>75</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>545</v>
+        <v>96</v>
       </c>
       <c r="L244" s="2"/>
-      <c r="M244" s="2"/>
+      <c r="M244" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="N244" s="2"/>
       <c r="O244" s="2"/>
       <c r="P244" t="s" s="2">
@@ -26873,13 +26941,13 @@
         <v>75</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>505</v>
+        <v>126</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH244" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI244" t="s" s="2">
         <v>75</v>
@@ -26893,10 +26961,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>507</v>
+        <v>477</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -26919,21 +26987,21 @@
         <v>75</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>508</v>
+        <v>86</v>
       </c>
       <c r="L245" s="2"/>
       <c r="M245" s="2"/>
       <c r="N245" s="2"/>
       <c r="O245" s="2"/>
       <c r="P245" t="s" s="2">
-        <v>75</v>
+        <v>478</v>
       </c>
       <c r="Q245" s="2"/>
       <c r="R245" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S245" t="s" s="2">
-        <v>75</v>
+        <v>478</v>
       </c>
       <c r="T245" t="s" s="2">
         <v>75</v>
@@ -26948,13 +27016,11 @@
         <v>75</v>
       </c>
       <c r="X245" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y245" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y245" s="2"/>
       <c r="Z245" t="s" s="2">
-        <v>75</v>
+        <v>479</v>
       </c>
       <c r="AA245" t="s" s="2">
         <v>75</v>
@@ -26972,7 +27038,7 @@
         <v>75</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>509</v>
+        <v>480</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>81</v>
@@ -26992,10 +27058,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -27018,7 +27084,7 @@
         <v>75</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>512</v>
+        <v>108</v>
       </c>
       <c r="L246" s="2"/>
       <c r="M246" s="2"/>
@@ -27029,7 +27095,7 @@
       </c>
       <c r="Q246" s="2"/>
       <c r="R246" t="s" s="2">
-        <v>75</v>
+        <v>483</v>
       </c>
       <c r="S246" t="s" s="2">
         <v>75</v>
@@ -27071,7 +27137,7 @@
         <v>75</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>81</v>
@@ -27091,10 +27157,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>515</v>
+        <v>486</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -27117,7 +27183,7 @@
         <v>75</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="L247" s="2"/>
       <c r="M247" s="2"/>
@@ -27170,7 +27236,7 @@
         <v>75</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>517</v>
+        <v>488</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>81</v>
@@ -27190,10 +27256,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -27216,7 +27282,7 @@
         <v>75</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="L248" s="2"/>
       <c r="M248" s="2"/>
@@ -27269,26 +27335,1016 @@
         <v>75</v>
       </c>
       <c r="AF248" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG248" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK248" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="249" hidden="true">
+      <c r="A249" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C249" s="2"/>
+      <c r="D249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E249" s="2"/>
+      <c r="F249" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K249" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L249" s="2"/>
+      <c r="M249" s="2"/>
+      <c r="N249" s="2"/>
+      <c r="O249" s="2"/>
+      <c r="P249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q249" s="2"/>
+      <c r="R249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF249" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG249" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK249" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="250" hidden="true">
+      <c r="A250" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C250" s="2"/>
+      <c r="D250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E250" s="2"/>
+      <c r="F250" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K250" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L250" s="2"/>
+      <c r="M250" s="2"/>
+      <c r="N250" s="2"/>
+      <c r="O250" s="2"/>
+      <c r="P250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q250" s="2"/>
+      <c r="R250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF250" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG250" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK250" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="251" hidden="true">
+      <c r="A251" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C251" s="2"/>
+      <c r="D251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E251" s="2"/>
+      <c r="F251" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K251" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L251" s="2"/>
+      <c r="M251" s="2"/>
+      <c r="N251" s="2"/>
+      <c r="O251" s="2"/>
+      <c r="P251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q251" s="2"/>
+      <c r="R251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF251" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG251" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK251" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="252" hidden="true">
+      <c r="A252" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C252" s="2"/>
+      <c r="D252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E252" s="2"/>
+      <c r="F252" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K252" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L252" s="2"/>
+      <c r="M252" s="2"/>
+      <c r="N252" s="2"/>
+      <c r="O252" s="2"/>
+      <c r="P252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q252" s="2"/>
+      <c r="R252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF252" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG252" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK252" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="253" hidden="true">
+      <c r="A253" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C253" s="2"/>
+      <c r="D253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E253" s="2"/>
+      <c r="F253" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K253" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L253" s="2"/>
+      <c r="M253" s="2"/>
+      <c r="N253" s="2"/>
+      <c r="O253" s="2"/>
+      <c r="P253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q253" s="2"/>
+      <c r="R253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF253" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AG253" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ253" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK253" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="254" hidden="true">
+      <c r="A254" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C254" s="2"/>
+      <c r="D254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E254" s="2"/>
+      <c r="F254" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K254" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L254" s="2"/>
+      <c r="M254" s="2"/>
+      <c r="N254" s="2"/>
+      <c r="O254" s="2"/>
+      <c r="P254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q254" s="2"/>
+      <c r="R254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF254" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AG254" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ254" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK254" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="255" hidden="true">
+      <c r="A255" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C255" s="2"/>
+      <c r="D255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E255" s="2"/>
+      <c r="F255" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K255" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L255" s="2"/>
+      <c r="M255" s="2"/>
+      <c r="N255" s="2"/>
+      <c r="O255" s="2"/>
+      <c r="P255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q255" s="2"/>
+      <c r="R255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF255" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG255" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ255" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK255" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="256" hidden="true">
+      <c r="A256" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B256" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AG248" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH248" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI248" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ248" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK248" t="s" s="2">
+      <c r="C256" s="2"/>
+      <c r="D256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E256" s="2"/>
+      <c r="F256" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K256" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="L256" s="2"/>
+      <c r="M256" s="2"/>
+      <c r="N256" s="2"/>
+      <c r="O256" s="2"/>
+      <c r="P256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q256" s="2"/>
+      <c r="R256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF256" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG256" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ256" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK256" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="257" hidden="true">
+      <c r="A257" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B257" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C257" s="2"/>
+      <c r="D257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E257" s="2"/>
+      <c r="F257" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K257" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="L257" s="2"/>
+      <c r="M257" s="2"/>
+      <c r="N257" s="2"/>
+      <c r="O257" s="2"/>
+      <c r="P257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q257" s="2"/>
+      <c r="R257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF257" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG257" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ257" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK257" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="258" hidden="true">
+      <c r="A258" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C258" s="2"/>
+      <c r="D258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E258" s="2"/>
+      <c r="F258" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K258" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="L258" s="2"/>
+      <c r="M258" s="2"/>
+      <c r="N258" s="2"/>
+      <c r="O258" s="2"/>
+      <c r="P258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q258" s="2"/>
+      <c r="R258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF258" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AG258" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ258" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK258" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK248">
+  <autoFilter ref="A1:AK258">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -27298,7 +28354,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI247">
+  <conditionalFormatting sqref="A2:AI257">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:38:58+00:00</t>
+    <t>2026-09-04T10:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:07:56+00:00</t>
+    <t>2026-09-08T08:30:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T08:30:09+00:00</t>
+    <t>2026-09-10T13:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
